--- a/game20 - 游戏源定时更新/web.xlsx
+++ b/game20 - 游戏源定时更新/web.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\object\projectGames\game20\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\object\projectGames\game20 - 游戏源定时更新\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="19140" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="7" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>domain</t>
   </si>
@@ -50,16 +50,10 @@
     <t>json</t>
   </si>
   <si>
-    <t>play.voidspire.cloud</t>
-  </si>
-  <si>
-    <t>#ed6d46</t>
-  </si>
-  <si>
-    <t>sec.voidspire.cloud</t>
-  </si>
-  <si>
-    <t>#7d929f</t>
+    <t>sec.faille.cloud</t>
+  </si>
+  <si>
+    <t>#1c579b</t>
   </si>
   <si>
     <t>paly.sorrel.cloud</t>
@@ -185,6 +179,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF2972F4"/>
@@ -193,13 +194,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="9"/>
       <color rgb="FF0000FF"/>
@@ -452,7 +446,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFED6D46"/>
+        <fgColor rgb="FF1C579B"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -936,7 +930,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -989,13 +983,16 @@
     <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1431,32 +1428,22 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
+      <c r="A3" s="20"/>
+      <c r="B3" s="21"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="21"/>
-      <c r="B4" s="22"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="23"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="21"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="21"/>
+      <c r="A5" s="22"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="22"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="21"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="21"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1492,10 +1479,10 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1506,10 +1493,10 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1520,10 +1507,10 @@
     </row>
     <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1532,20 +1519,20 @@
         <v>3</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="I5" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:10">
@@ -1553,10 +1540,10 @@
       <c r="B6" s="4"/>
       <c r="C6" s="9"/>
       <c r="I6" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:10">
@@ -1566,10 +1553,10 @@
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="I7" s="12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1579,10 +1566,10 @@
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="I8" s="14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1592,10 +1579,10 @@
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="I9" s="16" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10">
